--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260802_204505.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260802_204505.xlsx
@@ -6544,7 +6544,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6844,7 +6844,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7070,7 +7070,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260802_204505.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260802_204505.xlsx
@@ -5706,7 +5706,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6244,7 +6244,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6544,7 +6544,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6844,7 +6844,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7070,7 +7070,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260802_204505.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260802_204505.xlsx
@@ -5706,7 +5706,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6244,7 +6244,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260802_204505.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260802_204505.xlsx
@@ -5706,7 +5706,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6244,7 +6244,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8364,7 +8364,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8440,7 +8440,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8516,7 +8516,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260802_204505.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260802_204505.xlsx
@@ -6544,7 +6544,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6844,7 +6844,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7070,7 +7070,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8364,7 +8364,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8440,7 +8440,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8516,7 +8516,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260802_204505.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260802_204505.xlsx
@@ -5706,7 +5706,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6244,7 +6244,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6544,7 +6544,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6844,7 +6844,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7070,7 +7070,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260802_204505.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260802_204505.xlsx
@@ -8364,7 +8364,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8440,7 +8440,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8516,7 +8516,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260802_204505.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260802_204505.xlsx
@@ -5706,7 +5706,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6244,7 +6244,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6544,7 +6544,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6844,7 +6844,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7070,7 +7070,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8364,7 +8364,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8440,7 +8440,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8516,7 +8516,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260802_204505.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260802_204505.xlsx
@@ -6544,7 +6544,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6844,7 +6844,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7070,7 +7070,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8364,7 +8364,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8440,7 +8440,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8516,7 +8516,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260802_204505.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260802_204505.xlsx
@@ -8364,7 +8364,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8440,7 +8440,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8516,7 +8516,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260802_204505.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260802_204505.xlsx
@@ -6544,7 +6544,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6844,7 +6844,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7070,7 +7070,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260802_204505.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260802_204505.xlsx
@@ -5706,7 +5706,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6244,7 +6244,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6544,7 +6544,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6844,7 +6844,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7070,7 +7070,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8364,7 +8364,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8440,7 +8440,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8516,7 +8516,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260802_204505.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260802_204505.xlsx
@@ -5706,7 +5706,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6244,7 +6244,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8364,7 +8364,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8440,7 +8440,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8516,7 +8516,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260802_204505.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260802_204505.xlsx
@@ -5706,7 +5706,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6244,7 +6244,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6544,7 +6544,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6844,7 +6844,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7070,7 +7070,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260802_204505.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260802_204505.xlsx
@@ -5706,7 +5706,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6244,7 +6244,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6544,7 +6544,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6844,7 +6844,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7070,7 +7070,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260802_204505.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260802_204505.xlsx
@@ -5706,7 +5706,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6244,7 +6244,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6544,7 +6544,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6844,7 +6844,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7070,7 +7070,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8364,7 +8364,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8440,7 +8440,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8516,7 +8516,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
